--- a/research/traditional_assets/database/data/france/france_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/france/france_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.030935</v>
+        <v>0.05195</v>
       </c>
       <c r="E2">
-        <v>0.14455</v>
+        <v>0.1645</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,91 +606,91 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>54.91</v>
+        <v>74.66</v>
       </c>
       <c r="L2">
-        <v>0.05415187376725838</v>
+        <v>0.07554386319943338</v>
       </c>
       <c r="M2">
-        <v>28.9645</v>
+        <v>32.23</v>
       </c>
       <c r="N2">
-        <v>0.04793859649122807</v>
+        <v>0.05328153413787404</v>
       </c>
       <c r="O2">
-        <v>0.5274904389000182</v>
+        <v>0.4316903294937049</v>
       </c>
       <c r="P2">
-        <v>24.9745</v>
+        <v>24.16</v>
       </c>
       <c r="Q2">
-        <v>0.04133482290632241</v>
+        <v>0.03994048603074889</v>
       </c>
       <c r="R2">
-        <v>0.4548260790384265</v>
+        <v>0.323600321457273</v>
       </c>
       <c r="S2">
-        <v>3.989999999999998</v>
+        <v>8.07</v>
       </c>
       <c r="T2">
-        <v>0.1377548378187091</v>
+        <v>0.2503878374185541</v>
       </c>
       <c r="U2">
-        <v>520.2</v>
+        <v>425</v>
       </c>
       <c r="V2">
-        <v>0.8609731876861967</v>
+        <v>0.7025954703256737</v>
       </c>
       <c r="W2">
-        <v>0.1078841692411569</v>
+        <v>0.1179085843366945</v>
       </c>
       <c r="X2">
-        <v>0.0501432036234227</v>
+        <v>0.09501137936950138</v>
       </c>
       <c r="Y2">
-        <v>0.0577409656177342</v>
+        <v>0.02289720496719315</v>
       </c>
       <c r="Z2">
-        <v>1.601389766266582</v>
+        <v>1.622557872270564</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03537990309907632</v>
+        <v>0.0666472427242385</v>
       </c>
       <c r="AC2">
-        <v>-0.03537990309907632</v>
+        <v>-0.0666472427242385</v>
       </c>
       <c r="AD2">
-        <v>708.8</v>
+        <v>799.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>708.8</v>
+        <v>799.3</v>
       </c>
       <c r="AG2">
-        <v>188.5999999999999</v>
+        <v>374.3</v>
       </c>
       <c r="AH2">
-        <v>0.5398324447829398</v>
+        <v>0.5692209087024641</v>
       </c>
       <c r="AI2">
-        <v>0.5066838230037887</v>
+        <v>0.5490829154358728</v>
       </c>
       <c r="AJ2">
-        <v>0.2378910191725529</v>
+        <v>0.382250816993464</v>
       </c>
       <c r="AK2">
-        <v>0.2146352566291111</v>
+        <v>0.3631512564276705</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-2.64</v>
+        <v>-1.69</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00967</v>
+        <v>0.0344</v>
       </c>
       <c r="E3">
-        <v>0.0431</v>
+        <v>0.142</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,91 +731,91 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>47.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="L3">
-        <v>0.04927083333333333</v>
+        <v>0.07204518810614942</v>
       </c>
       <c r="M3">
-        <v>25.69</v>
+        <v>28.17</v>
       </c>
       <c r="N3">
-        <v>0.05939884393063583</v>
+        <v>0.06986607142857143</v>
       </c>
       <c r="O3">
-        <v>0.5431289640591966</v>
+        <v>0.416715976331361</v>
       </c>
       <c r="P3">
-        <v>21.7</v>
+        <v>20.1</v>
       </c>
       <c r="Q3">
-        <v>0.05017341040462427</v>
+        <v>0.04985119047619048</v>
       </c>
       <c r="R3">
-        <v>0.4587737843551797</v>
+        <v>0.2973372781065089</v>
       </c>
       <c r="S3">
-        <v>3.989999999999998</v>
+        <v>8.07</v>
       </c>
       <c r="T3">
-        <v>0.1553133514986376</v>
+        <v>0.2864749733759319</v>
       </c>
       <c r="U3">
-        <v>520.2</v>
+        <v>425</v>
       </c>
       <c r="V3">
-        <v>1.202774566473989</v>
+        <v>1.05406746031746</v>
       </c>
       <c r="W3">
-        <v>0.112511893434824</v>
+        <v>0.1484409310496267</v>
       </c>
       <c r="X3">
-        <v>0.05693735425895117</v>
+        <v>0.1108356082417571</v>
       </c>
       <c r="Y3">
-        <v>0.0555745391758728</v>
+        <v>0.03760532280786957</v>
       </c>
       <c r="Z3">
-        <v>2.175390890550646</v>
+        <v>2.058126782189078</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03535034969221103</v>
+        <v>0.06551080686131799</v>
       </c>
       <c r="AC3">
-        <v>-0.03535034969221103</v>
+        <v>-0.06551080686131799</v>
       </c>
       <c r="AD3">
-        <v>618.8</v>
+        <v>716.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>618.8</v>
+        <v>716.5</v>
       </c>
       <c r="AG3">
-        <v>98.59999999999991</v>
+        <v>291.5</v>
       </c>
       <c r="AH3">
-        <v>0.5886045847997717</v>
+        <v>0.6399035455925695</v>
       </c>
       <c r="AI3">
-        <v>0.5038677632114649</v>
+        <v>0.5498848810437452</v>
       </c>
       <c r="AJ3">
-        <v>0.1856524195066841</v>
+        <v>0.4196055851446667</v>
       </c>
       <c r="AK3">
-        <v>0.1392852097753919</v>
+        <v>0.332004555808656</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-2.64</v>
+        <v>-1.69</v>
       </c>
       <c r="AQ3">
         <v>-0</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0522</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="E4">
-        <v>0.246</v>
+        <v>0.187</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>7.61</v>
+        <v>7.06</v>
       </c>
       <c r="L4">
-        <v>0.1409259259259259</v>
+        <v>0.1412</v>
       </c>
       <c r="M4">
-        <v>3.2745</v>
+        <v>4.06</v>
       </c>
       <c r="N4">
-        <v>0.01907105416423995</v>
+        <v>0.02012890431333664</v>
       </c>
       <c r="O4">
-        <v>0.4302890932982917</v>
+        <v>0.575070821529745</v>
       </c>
       <c r="P4">
-        <v>3.2745</v>
+        <v>4.06</v>
       </c>
       <c r="Q4">
-        <v>0.01907105416423995</v>
+        <v>0.02012890431333664</v>
       </c>
       <c r="R4">
-        <v>0.4302890932982917</v>
+        <v>0.575070821529745</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,49 +892,49 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.1032564450474898</v>
+        <v>0.08737623762376237</v>
       </c>
       <c r="X4">
-        <v>0.04334905298789424</v>
+        <v>0.07918715049724565</v>
       </c>
       <c r="Y4">
-        <v>0.05990739205959558</v>
+        <v>0.008189087126516725</v>
       </c>
       <c r="Z4">
-        <v>0.2813965607087025</v>
+        <v>0.3263707571801566</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03540945650594161</v>
+        <v>0.06778367858715902</v>
       </c>
       <c r="AC4">
-        <v>-0.03540945650594161</v>
+        <v>-0.06778367858715902</v>
       </c>
       <c r="AD4">
-        <v>90</v>
+        <v>82.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>90</v>
+        <v>82.8</v>
       </c>
       <c r="AG4">
-        <v>90</v>
+        <v>82.8</v>
       </c>
       <c r="AH4">
-        <v>0.3439052350019106</v>
+        <v>0.29103690685413</v>
       </c>
       <c r="AI4">
-        <v>0.5269320843091334</v>
+        <v>0.5422396856581533</v>
       </c>
       <c r="AJ4">
-        <v>0.3439052350019106</v>
+        <v>0.29103690685413</v>
       </c>
       <c r="AK4">
-        <v>0.5269320843091334</v>
+        <v>0.5422396856581533</v>
       </c>
       <c r="AL4">
         <v>0</v>

--- a/research/traditional_assets/database/data/france/france_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/france/france_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05195</v>
+        <v>0.08135000000000001</v>
       </c>
       <c r="E2">
-        <v>0.1645</v>
+        <v>0.226</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,91 +606,91 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>74.66</v>
+        <v>101.3</v>
       </c>
       <c r="L2">
-        <v>0.07554386319943338</v>
+        <v>0.08527653842916069</v>
       </c>
       <c r="M2">
-        <v>32.23</v>
+        <v>32.1</v>
       </c>
       <c r="N2">
-        <v>0.05328153413787404</v>
+        <v>0.03537190082644628</v>
       </c>
       <c r="O2">
-        <v>0.4316903294937049</v>
+        <v>0.3168805528134255</v>
       </c>
       <c r="P2">
-        <v>24.16</v>
+        <v>28.82</v>
       </c>
       <c r="Q2">
-        <v>0.03994048603074889</v>
+        <v>0.03175757575757576</v>
       </c>
       <c r="R2">
-        <v>0.323600321457273</v>
+        <v>0.2845014807502468</v>
       </c>
       <c r="S2">
-        <v>8.07</v>
+        <v>3.280000000000001</v>
       </c>
       <c r="T2">
-        <v>0.2503878374185541</v>
+        <v>0.1021806853582555</v>
       </c>
       <c r="U2">
-        <v>425</v>
+        <v>466.3</v>
       </c>
       <c r="V2">
-        <v>0.7025954703256737</v>
+        <v>0.5138292011019284</v>
       </c>
       <c r="W2">
-        <v>0.1179085843366945</v>
+        <v>0.1832394197813579</v>
       </c>
       <c r="X2">
-        <v>0.09501137936950138</v>
+        <v>0.06731449849335377</v>
       </c>
       <c r="Y2">
-        <v>0.02289720496719315</v>
+        <v>0.1159249212880041</v>
       </c>
       <c r="Z2">
-        <v>1.622557872270564</v>
+        <v>1.553013465812525</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0666472427242385</v>
+        <v>0.05749409734400334</v>
       </c>
       <c r="AC2">
-        <v>-0.0666472427242385</v>
+        <v>-0.05749409734400334</v>
       </c>
       <c r="AD2">
-        <v>799.3</v>
+        <v>551.3000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>799.3</v>
+        <v>551.3000000000001</v>
       </c>
       <c r="AG2">
-        <v>374.3</v>
+        <v>85.00000000000006</v>
       </c>
       <c r="AH2">
-        <v>0.5692209087024641</v>
+        <v>0.3779133534411845</v>
       </c>
       <c r="AI2">
-        <v>0.5490829154358728</v>
+        <v>0.433071484681854</v>
       </c>
       <c r="AJ2">
-        <v>0.382250816993464</v>
+        <v>0.0856423173803527</v>
       </c>
       <c r="AK2">
-        <v>0.3631512564276705</v>
+        <v>0.105367546795587</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1.69</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0344</v>
+        <v>0.0635</v>
       </c>
       <c r="E3">
-        <v>0.142</v>
+        <v>0.194</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -731,91 +731,91 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>67.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="L3">
-        <v>0.07204518810614942</v>
+        <v>0.08002129169623846</v>
       </c>
       <c r="M3">
-        <v>28.17</v>
+        <v>27.58</v>
       </c>
       <c r="N3">
-        <v>0.06986607142857143</v>
+        <v>0.04616672246401072</v>
       </c>
       <c r="O3">
-        <v>0.416715976331361</v>
+        <v>0.3057649667405765</v>
       </c>
       <c r="P3">
-        <v>20.1</v>
+        <v>24.3</v>
       </c>
       <c r="Q3">
-        <v>0.04985119047619048</v>
+        <v>0.04067626380984266</v>
       </c>
       <c r="R3">
-        <v>0.2973372781065089</v>
+        <v>0.2694013303769401</v>
       </c>
       <c r="S3">
-        <v>8.07</v>
+        <v>3.280000000000001</v>
       </c>
       <c r="T3">
-        <v>0.2864749733759319</v>
+        <v>0.1189267585206672</v>
       </c>
       <c r="U3">
-        <v>425</v>
+        <v>466.3</v>
       </c>
       <c r="V3">
-        <v>1.05406746031746</v>
+        <v>0.7805490458654168</v>
       </c>
       <c r="W3">
-        <v>0.1484409310496267</v>
+        <v>0.2058420812414423</v>
       </c>
       <c r="X3">
-        <v>0.1108356082417571</v>
+        <v>0.07197679289686362</v>
       </c>
       <c r="Y3">
-        <v>0.03760532280786957</v>
+        <v>0.1338652883445786</v>
       </c>
       <c r="Z3">
-        <v>2.058126782189078</v>
+        <v>1.775118110236221</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06551080686131799</v>
+        <v>0.05665078638025003</v>
       </c>
       <c r="AC3">
-        <v>-0.06551080686131799</v>
+        <v>-0.05665078638025003</v>
       </c>
       <c r="AD3">
-        <v>716.5</v>
+        <v>486.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>716.5</v>
+        <v>486.1</v>
       </c>
       <c r="AG3">
-        <v>291.5</v>
+        <v>19.80000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.6399035455925695</v>
+        <v>0.4486386709736964</v>
       </c>
       <c r="AI3">
-        <v>0.5498848810437452</v>
+        <v>0.4301389257587825</v>
       </c>
       <c r="AJ3">
-        <v>0.4196055851446667</v>
+        <v>0.03208036292935841</v>
       </c>
       <c r="AK3">
-        <v>0.332004555808656</v>
+        <v>0.02982826152455561</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1.69</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="AQ3">
         <v>-0</v>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.06950000000000001</v>
+        <v>0.0992</v>
       </c>
       <c r="E4">
-        <v>0.187</v>
+        <v>0.258</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -856,28 +856,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>7.06</v>
+        <v>11.1</v>
       </c>
       <c r="L4">
-        <v>0.1412</v>
+        <v>0.1828665568369028</v>
       </c>
       <c r="M4">
-        <v>4.06</v>
+        <v>4.52</v>
       </c>
       <c r="N4">
-        <v>0.02012890431333664</v>
+        <v>0.0145759432441148</v>
       </c>
       <c r="O4">
-        <v>0.575070821529745</v>
+        <v>0.4072072072072072</v>
       </c>
       <c r="P4">
-        <v>4.06</v>
+        <v>4.52</v>
       </c>
       <c r="Q4">
-        <v>0.02012890431333664</v>
+        <v>0.0145759432441148</v>
       </c>
       <c r="R4">
-        <v>0.575070821529745</v>
+        <v>0.4072072072072072</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,49 +892,49 @@
         <v>0</v>
       </c>
       <c r="W4">
-        <v>0.08737623762376237</v>
+        <v>0.1606367583212735</v>
       </c>
       <c r="X4">
-        <v>0.07918715049724565</v>
+        <v>0.06265220408984393</v>
       </c>
       <c r="Y4">
-        <v>0.008189087126516725</v>
+        <v>0.0979845542314296</v>
       </c>
       <c r="Z4">
-        <v>0.3263707571801566</v>
+        <v>0.4672825250192457</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06778367858715902</v>
+        <v>0.05833740830775665</v>
       </c>
       <c r="AC4">
-        <v>-0.06778367858715902</v>
+        <v>-0.05833740830775665</v>
       </c>
       <c r="AD4">
-        <v>82.8</v>
+        <v>65.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>82.8</v>
+        <v>65.2</v>
       </c>
       <c r="AG4">
-        <v>82.8</v>
+        <v>65.2</v>
       </c>
       <c r="AH4">
-        <v>0.29103690685413</v>
+        <v>0.1737276845190514</v>
       </c>
       <c r="AI4">
-        <v>0.5422396856581533</v>
+        <v>0.4562631210636809</v>
       </c>
       <c r="AJ4">
-        <v>0.29103690685413</v>
+        <v>0.1737276845190514</v>
       </c>
       <c r="AK4">
-        <v>0.5422396856581533</v>
+        <v>0.4562631210636809</v>
       </c>
       <c r="AL4">
         <v>0</v>
